--- a/results/exp09-c100-vgg11-e32-k12-posthoc/20260925-043635/rounds.xlsx
+++ b/results/exp09-c100-vgg11-e32-k12-posthoc/20260925-043635/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,6 +1611,836 @@
       <c r="U14" t="inlineStr">
         <is>
           <t>5.7214,4.8103,7.5965,6.9261,5.8277,7.4213,3.9636,5.2879,5.2216,4.1896</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:49:43</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.342213634524516</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="G15" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>57.7254</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0:57.73</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>56.5231</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.0524</v>
+      </c>
+      <c r="N15" t="n">
+        <v>788.1676</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>13:08.17</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2,4,5,1,7,0,9,3,8,6</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2:15;4:10;5:20;1:13;7:10;0:10;9:11;3:15;8:10;6:20</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2:[20];4:[20];5:[10,17];1:[20];7:[20];0:[20];9:[20];3:[20];8:[20];6:[17,20]</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>c2:bw=15,experts=[20]; c4:bw=10,experts=[20]; c5:bw=20,experts=[10,17]; c1:bw=13,experts=[20]; c7:bw=10,experts=[20]; c0:bw=10,experts=[20]; c9:bw=11,experts=[20]; c3:bw=15,experts=[20]; c8:bw=10,experts=[20]; c6:bw=20,experts=[17,20]</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4.1626,7.4855,6.6969,4.6666,5.0476,5.1896,3.9596,5.7558,6.0298,7.5291</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:50:41</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.305226694945799</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>57.7292</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0:57.73</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>56.5273</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.0507</v>
+      </c>
+      <c r="N16" t="n">
+        <v>846.1188</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>14:06.12</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>7,0,1,8,3,2,4,5,9,6</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>7:20;0:10;1:10;8:17;3:10;2:18;4:16;5:10;9:10;6:11</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>7:[17,20];0:[20];1:[20];8:[20];3:[20];2:[20];4:[20];5:[17];9:[20];6:[20]</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>c7:bw=20,experts=[17,20]; c0:bw=10,experts=[20]; c1:bw=10,experts=[20]; c8:bw=17,experts=[20]; c3:bw=10,experts=[20]; c2:bw=18,experts=[20]; c4:bw=16,experts=[20]; c5:bw=10,experts=[17]; c9:bw=10,experts=[20]; c6:bw=11,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5.1688,5.2221,4.6797,5.8833,5.6825,4.1414,7.5383,6.9119,3.8394,7.4599</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:51:38</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.269697910487817</v>
+      </c>
+      <c r="F17" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>57.1571</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0:57.16</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55.962</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.0498</v>
+      </c>
+      <c r="N17" t="n">
+        <v>903.2926</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>15:03.29</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>6,1,3,8,7,5,4,9,0,2</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6:13;1:10;3:14;8:16;7:10;5:13;4:12;9:10;0:19;2:17</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>6:[20];1:[20];3:[20];8:[20];7:[20];5:[17];4:[20];9:[20];0:[20];2:[20]</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>c6:bw=13,experts=[20]; c1:bw=10,experts=[20]; c3:bw=14,experts=[20]; c8:bw=16,experts=[20]; c7:bw=10,experts=[20]; c5:bw=13,experts=[17]; c4:bw=12,experts=[20]; c9:bw=10,experts=[20]; c0:bw=19,experts=[20]; c2:bw=17,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7.3487,4.6928,5.5027,5.8584,5.1068,6.7637,7.4839,3.9001,5.1098,4.1950</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:52:36</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.248118166737316</v>
+      </c>
+      <c r="F18" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="G18" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>57.3312</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0:57.33</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>56.1339</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.0444</v>
+      </c>
+      <c r="N18" t="n">
+        <v>960.6419</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>16:00.64</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4,7,8,3,5,1,0,2,9,6</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>4:19;7:10;8:10;3:17;5:10;1:10;0:10;2:10;9:12;6:13</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4:[20];7:[20];8:[20];3:[20];5:[17];1:[20];0:[20];2:[20];9:[20];6:[20]</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>c4:bw=19,experts=[20]; c7:bw=10,experts=[20]; c8:bw=10,experts=[20]; c3:bw=17,experts=[20]; c5:bw=10,experts=[17]; c1:bw=10,experts=[20]; c0:bw=10,experts=[20]; c2:bw=10,experts=[20]; c9:bw=12,experts=[20]; c6:bw=13,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>7.5278,4.9593,5.8343,5.5507,6.7288,4.8062,5.2105,4.1817,3.8109,7.5237</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:53:35</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.210602621408425</v>
+      </c>
+      <c r="F19" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" t="n">
+        <v>58.927</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0:58.93</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>57.6944</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.0735</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1019.5859</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>16:59.59</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1,8,5,2,9,7,4,3,0,6</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1:10;8:10;5:12;2:12;9:10;7:18;4:19;3:12;0:16;6:10</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1:[20];8:[20];5:[17];2:[20];9:[20];7:[20];4:[20];3:[20];0:[20];6:[20]</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[20]; c8:bw=10,experts=[20]; c5:bw=12,experts=[17]; c2:bw=12,experts=[20]; c9:bw=10,experts=[20]; c7:bw=18,experts=[20]; c4:bw=19,experts=[20]; c3:bw=12,experts=[20]; c0:bw=16,experts=[20]; c6:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>4.8474,5.9281,6.8055,4.1135,3.8528,5.1397,7.7472,6.1754,5.3421,7.7426</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:54:34</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.175738953332363</v>
+      </c>
+      <c r="F20" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="H20" t="n">
+        <v>19</v>
+      </c>
+      <c r="I20" t="n">
+        <v>59.5644</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0:59.56</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>58.3572</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.0603</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1079.1677</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>17:59.17</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>8,0,4,1,9,5,7,2,6,3</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>8:19;0:14;4:17;1:15;9:13;5:10;7:10;2:10;6:20;3:13</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>8:[20];0:[20];4:[20];1:[20];9:[20];5:[17];7:[20];2:[20];6:[17,20];3:[20]</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>c8:bw=19,experts=[20]; c0:bw=14,experts=[20]; c4:bw=17,experts=[20]; c1:bw=15,experts=[20]; c9:bw=13,experts=[20]; c5:bw=10,experts=[17]; c7:bw=10,experts=[20]; c2:bw=10,experts=[20]; c6:bw=20,experts=[17,20]; c3:bw=13,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6.2179,5.2757,7.6275,4.9370,4.1256,7.3098,5.2494,4.2848,7.4751,5.8543</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:55:35</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.15754078064873</v>
+      </c>
+      <c r="F21" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="G21" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>61.0328</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1:01.03</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>59.7547</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.1252</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1140.2208</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>19:00.22</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0,2,1,9,7,6,3,5,4,8</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0:10;2:14;1:13;9:10;7:14;6:20;3:10;5:10;4:20;8:17</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0:[20];2:[20];1:[20];9:[20];7:[20];6:[17,20];3:[20];5:[17];4:[17,20];8:[20]</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>c0:bw=10,experts=[20]; c2:bw=14,experts=[20]; c1:bw=13,experts=[20]; c9:bw=10,experts=[20]; c7:bw=14,experts=[20]; c6:bw=20,experts=[17,20]; c3:bw=10,experts=[20]; c5:bw=10,experts=[17]; c4:bw=20,experts=[17,20]; c8:bw=17,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>5.3935,4.3106,5.0119,4.0545,5.4437,8.0240,5.9353,7.2489,7.9625,6.3697</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:56:37</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.12894603010255</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="G22" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="H22" t="n">
+        <v>21</v>
+      </c>
+      <c r="I22" t="n">
+        <v>61.4407</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1:01.44</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>60.216</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.0783</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1201.6817</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>20:01.68</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1,2,7,4,8,5,0,3,6,9</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1:14;2:13;7:10;4:16;8:10;5:11;0:20;3:10;6:10;9:10</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1:[20];2:[20];7:[20];4:[20];8:[20];5:[17];0:[17,20];3:[20];6:[20];9:[20]</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>c1:bw=14,experts=[20]; c2:bw=13,experts=[20]; c7:bw=10,experts=[20]; c4:bw=16,experts=[20]; c8:bw=10,experts=[20]; c5:bw=11,experts=[17]; c0:bw=20,experts=[17,20]; c3:bw=10,experts=[20]; c6:bw=10,experts=[20]; c9:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>5.1400,4.3800,5.3720,8.0543,6.3742,7.3407,5.4429,5.9128,7.9357,4.2632</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:57:37</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.109101335955607</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="H23" t="n">
+        <v>21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>60.0305</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1:00.03</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>58.8301</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.0465</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1261.7306</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>21:01.73</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>7,9,1,6,5,2,0,4,3,8</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>7:10;9:11;1:10;6:20;5:10;2:20;0:20;4:12;3:19;8:11</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>7:[20];9:[20];1:[20];6:[17,20];5:[17];2:[17,20];0:[17,20];4:[20];3:[20];8:[20]</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[20]; c9:bw=11,experts=[20]; c1:bw=10,experts=[20]; c6:bw=20,experts=[17,20]; c5:bw=10,experts=[17]; c2:bw=20,experts=[17,20]; c0:bw=20,experts=[17,20]; c4:bw=12,experts=[20]; c3:bw=19,experts=[20]; c8:bw=11,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>5.3293,4.0737,5.0553,7.7591,7.0996,4.2637,5.3611,7.8542,5.9559,6.0780</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:58:37</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.085322786168713</v>
+      </c>
+      <c r="F24" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="G24" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="H24" t="n">
+        <v>23</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60.6497</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1:00.65</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>59.3872</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.1101</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1322.399</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>22:02.40</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5,7,4,6,9,8,3,1,2,0</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>5:17;7:10;4:19;6:10;9:17;8:12;3:10;1:20;2:11;0:10</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>5:[17];7:[20];4:[20];6:[20];9:[20];8:[20];3:[20];1:[17,20];2:[20];0:[20]</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>c5:bw=17,experts=[17]; c7:bw=10,experts=[20]; c4:bw=19,experts=[20]; c6:bw=10,experts=[20]; c9:bw=17,experts=[20]; c8:bw=12,experts=[20]; c3:bw=10,experts=[20]; c1:bw=20,experts=[17,20]; c2:bw=11,experts=[20]; c0:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>7.0093,5.2493,7.6290,7.8301,4.2499,6.2024,6.0856,5.1352,4.5083,5.4883</t>
         </is>
       </c>
     </row>

--- a/results/exp09-c100-vgg11-e32-k12-posthoc/20260925-043635/rounds.xlsx
+++ b/results/exp09-c100-vgg11-e32-k12-posthoc/20260925-043635/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,6 +2444,2081 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:59:39</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.073790719405458</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="H25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I25" t="n">
+        <v>61.6892</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1:01.69</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>60.4372</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.1127</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1384.1094</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>23:04.11</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6,4,7,9,2,1,5,8,3,0</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6:10;4:10;7:10;9:17;2:14;1:10;5:10;8:10;3:10;0:10</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>6:[20];4:[20];7:[20];9:[20];2:[20];1:[20];5:[17];8:[20];3:[20];0:[20]</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>c6:bw=10,experts=[20]; c4:bw=10,experts=[20]; c7:bw=10,experts=[20]; c9:bw=17,experts=[20]; c2:bw=14,experts=[20]; c1:bw=10,experts=[20]; c5:bw=10,experts=[17]; c8:bw=10,experts=[20]; c3:bw=10,experts=[20]; c0:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>7.9696,7.8974,5.3208,4.1900,4.4719,5.0344,7.3594,6.3708,6.2086,5.6141</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:00:44</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.047281522380181</v>
+      </c>
+      <c r="F26" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="G26" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="H26" t="n">
+        <v>25</v>
+      </c>
+      <c r="I26" t="n">
+        <v>64.70489999999999</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1:04.70</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>63.4781</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.0795</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1448.9391</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>24:08.94</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>9,6,4,3,5,1,8,2,0,7</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>9:13;6:10;4:19;3:10;5:20;1:16;8:18;2:10;0:19;7:13</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>9:[20];6:[20];4:[20];3:[20];5:[10,17];1:[20];8:[20];2:[20];0:[20];7:[20]</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>c9:bw=13,experts=[20]; c6:bw=10,experts=[20]; c4:bw=19,experts=[20]; c3:bw=10,experts=[20]; c5:bw=20,experts=[10,17]; c1:bw=16,experts=[20]; c8:bw=18,experts=[20]; c2:bw=10,experts=[20]; c0:bw=19,experts=[20]; c7:bw=13,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>4.2445,7.8672,8.8096,6.8241,7.9454,4.9608,6.3852,4.8448,6.0511,5.5454</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:01:44</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.028058416307069</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="G27" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="H27" t="n">
+        <v>26</v>
+      </c>
+      <c r="I27" t="n">
+        <v>59.8243</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0:59.82</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>58.5931</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.0907</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1508.7873</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>25:08.79</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3,6,9,7,1,5,2,8,0,4</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3:15;6:11;9:17;7:10;1:11;5:10;2:10;8:18;0:10;4:16</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3:[20];6:[20];9:[20];7:[20];1:[20];5:[17];2:[20];8:[20];0:[20];4:[20]</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>c3:bw=15,experts=[20]; c6:bw=11,experts=[20]; c9:bw=17,experts=[20]; c7:bw=10,experts=[20]; c1:bw=11,experts=[20]; c5:bw=10,experts=[17]; c2:bw=10,experts=[20]; c8:bw=18,experts=[20]; c0:bw=10,experts=[20]; c4:bw=16,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>5.7580,7.3719,3.9370,5.1012,4.7649,7.0798,4.4411,6.4410,5.6799,8.0182</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:02:45</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.014209278660478</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="G28" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="H28" t="n">
+        <v>26</v>
+      </c>
+      <c r="I28" t="n">
+        <v>60.9615</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1:00.96</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>59.7189</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.0993</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1569.7704</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>26:09.77</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>7,1,4,0,9,2,8,3,6,5</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>7:17;1:20;4:10;0:12;9:10;2:10;8:18;3:10;6:20;5:12</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>7:[20];1:[17,20];4:[20];0:[20];9:[20];2:[20];8:[20];3:[20];6:[17,20];5:[17]</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>c7:bw=17,experts=[20]; c1:bw=20,experts=[17,20]; c4:bw=10,experts=[20]; c0:bw=12,experts=[20]; c9:bw=10,experts=[20]; c2:bw=10,experts=[20]; c8:bw=18,experts=[20]; c3:bw=10,experts=[20]; c6:bw=20,experts=[17,20]; c5:bw=12,experts=[17]</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>5.4199,4.9964,7.7522,5.3532,4.2145,4.4558,6.3820,6.1598,7.7763,7.2088</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:03:46</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.996379141207884</v>
+      </c>
+      <c r="F29" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="G29" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="H29" t="n">
+        <v>28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>60.966</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1:00.97</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>59.7474</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.0745</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1630.7572</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>27:10.76</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6,9,0,8,2,5,1,3,4,7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6:10;9:16;0:16;8:10;2:10;5:11;1:10;3:10;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>6:[20];9:[20];0:[20];8:[20];2:[20];5:[17];1:[20];3:[20];4:[20];7:[20]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>c6:bw=10,experts=[20]; c9:bw=16,experts=[20]; c0:bw=16,experts=[20]; c8:bw=10,experts=[20]; c2:bw=10,experts=[20]; c5:bw=11,experts=[17]; c1:bw=10,experts=[20]; c3:bw=10,experts=[20]; c4:bw=10,experts=[20]; c7:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>7.6749,4.1310,5.3913,6.2736,4.4986,7.6004,5.2094,5.9392,7.7293,5.2998</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:04:46</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.990110725631757</v>
+      </c>
+      <c r="F30" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="G30" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="H30" t="n">
+        <v>29</v>
+      </c>
+      <c r="I30" t="n">
+        <v>59.9875</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0:59.99</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>58.7442</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.0776</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1690.766</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>28:10.77</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4,0,1,9,6,8,7,3,2,5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4:13;0:15;1:11;9:15;6:14;8:11;7:10;3:11;2:10;5:11</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4:[20];0:[20];1:[20];9:[20];6:[20];8:[20];7:[20];3:[20];2:[20];5:[20]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>c4:bw=13,experts=[20]; c0:bw=15,experts=[20]; c1:bw=11,experts=[20]; c9:bw=15,experts=[20]; c6:bw=14,experts=[20]; c8:bw=11,experts=[20]; c7:bw=10,experts=[20]; c3:bw=11,experts=[20]; c2:bw=10,experts=[20]; c5:bw=11,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>7.5747,5.3128,4.9762,4.0726,7.7230,6.1835,5.2619,5.9476,4.4117,7.2802</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:05:47</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.968846239662316</v>
+      </c>
+      <c r="F31" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="G31" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="H31" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" t="n">
+        <v>61.3799</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1:01.38</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>60.1175</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.1039</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1752.1671</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>29:12.17</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:20;1:12;9:18;4:17;0:10;8:14;6:10;7:10;3:20;2:10</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[17,20];1:[20];9:[20];4:[20];0:[20];8:[20];6:[20];7:[20];3:[17,20];2:[20]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=20,experts=[17,20]; c1:bw=12,experts=[20]; c9:bw=18,experts=[20]; c4:bw=17,experts=[20]; c0:bw=10,experts=[20]; c8:bw=14,experts=[20]; c6:bw=10,experts=[20]; c7:bw=10,experts=[20]; c3:bw=20,experts=[17,20]; c2:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>7.1792,5.0375,4.1316,8.1420,5.6651,6.3710,7.8025,5.3989,5.9760,4.4138</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:06:47</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.955532975469499</v>
+      </c>
+      <c r="F32" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="H32" t="n">
+        <v>31</v>
+      </c>
+      <c r="I32" t="n">
+        <v>59.4053</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0:59.41</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>58.2079</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.0407</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1811.597</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>30:11.60</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:10;4:10;9:15;1:10;5:20;8:11;3:10;2:10;0:16;7:20</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[20];4:[20];9:[20];1:[20];5:[10,17];8:[20];3:[20];2:[20];0:[20];7:[17,20]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=10,experts=[20]; c4:bw=10,experts=[20]; c9:bw=15,experts=[20]; c1:bw=10,experts=[20]; c5:bw=20,experts=[10,17]; c8:bw=11,experts=[20]; c3:bw=10,experts=[20]; c2:bw=10,experts=[20]; c0:bw=16,experts=[20]; c7:bw=20,experts=[17,20]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>7.6187,7.7084,4.1295,5.1003,7.1099,5.9941,5.7539,4.3473,5.3393,5.1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:07:48</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.93170552362331</v>
+      </c>
+      <c r="F33" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="G33" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32</v>
+      </c>
+      <c r="I33" t="n">
+        <v>60.9651</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1:00.97</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>59.7075</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1549</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1017</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1872.5835</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>31:12.58</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:10;5:12;4:16;7:16;0:15;1:10;3:10;6:10;2:18;9:10</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[0];5:[0];4:[0];7:[0];0:[0];1:[0];3:[1];6:[0];2:[0];9:[1]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[0]; c5:bw=12,experts=[0]; c4:bw=16,experts=[0]; c7:bw=16,experts=[0]; c0:bw=15,experts=[0]; c1:bw=10,experts=[0]; c3:bw=10,experts=[1]; c6:bw=10,experts=[0]; c2:bw=18,experts=[0]; c9:bw=10,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>5.8778,7.1284,8.0948,5.5080,5.5308,5.0918,6.0632,7.8436,4.4301,4.1390</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:08:50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.915611321424984</v>
+      </c>
+      <c r="F34" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="G34" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>61.9182</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1:01.92</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>60.6302</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.1227</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1934.5224</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>32:14.52</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:17;1:11;3:20;6:12;5:10;9:14;2:10;8:17;4:15;0:20</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[1];1:[1];3:[2,3];6:[1];5:[1];9:[2];2:[1];8:[1];4:[1];0:[1,2]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=17,experts=[1]; c1:bw=11,experts=[1]; c3:bw=20,experts=[2,3]; c6:bw=12,experts=[1]; c5:bw=10,experts=[1]; c9:bw=14,experts=[2]; c2:bw=10,experts=[1]; c8:bw=17,experts=[1]; c4:bw=15,experts=[1]; c0:bw=20,experts=[1,2]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>5.3625,5.2327,6.3110,8.0745,7.3774,4.0790,4.3399,6.3365,8.0612,5.4555</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:09:50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.907363217837993</v>
+      </c>
+      <c r="F35" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>60.2169</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1:00.22</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>58.9637</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.0986</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1994.7638</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>33:14.76</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:15;1:15;6:16;9:20;8:14;0:10;5:20;7:11;3:20;2:18</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[2];1:[2];6:[2];9:[3,4];8:[2];0:[3];5:[2,3];7:[2];3:[4,5];2:[2]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=15,experts=[2]; c1:bw=15,experts=[2]; c6:bw=16,experts=[2]; c9:bw=20,experts=[3,4]; c8:bw=14,experts=[2]; c0:bw=10,experts=[3]; c5:bw=20,experts=[2,3]; c7:bw=11,experts=[2]; c3:bw=20,experts=[4,5]; c2:bw=18,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7.9829,5.2083,7.9281,4.0922,6.0581,5.3510,6.9843,5.1739,5.7432,4.4416</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:10:50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.894827638878748</v>
+      </c>
+      <c r="F36" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="G36" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="H36" t="n">
+        <v>35</v>
+      </c>
+      <c r="I36" t="n">
+        <v>60.6058</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1:00.61</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>59.3243</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.1095</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2055.3938</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>34:15.39</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:11;0:10;1:10;6:15;2:15;8:17;9:10;7:16;5:14;3:10</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[3];0:[4];1:[3];6:[3];2:[3];8:[3];9:[5];7:[3];5:[4];3:[6]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=11,experts=[3]; c0:bw=10,experts=[4]; c1:bw=10,experts=[3]; c6:bw=15,experts=[3]; c2:bw=15,experts=[3]; c8:bw=17,experts=[3]; c9:bw=10,experts=[5]; c7:bw=16,experts=[3]; c5:bw=14,experts=[4]; c3:bw=10,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7.7806,5.3144,5.0403,7.7182,4.3150,6.2287,4.0669,5.3571,7.3641,6.1391</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:11:51</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.883456766095884</v>
+      </c>
+      <c r="F37" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="G37" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>60.0615</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1:00.06</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>58.8687</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.0424</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2115.485</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>35:15.49</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:12;0:12;3:20;7:10;6:14;5:16;1:10;4:20;8:17;2:17</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[6];0:[5];3:[7,8];7:[4];6:[4];5:[5];1:[4];4:[4,5];8:[4];2:[4]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=12,experts=[6]; c0:bw=12,experts=[5]; c3:bw=20,experts=[7,8]; c7:bw=10,experts=[4]; c6:bw=14,experts=[4]; c5:bw=16,experts=[5]; c1:bw=10,experts=[4]; c4:bw=20,experts=[4,5]; c8:bw=17,experts=[4]; c2:bw=17,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>4.2666,5.5423,6.0886,5.3540,7.5636,7.0027,4.8756,7.7778,6.1526,4.2449</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:12:52</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.87839961043008</v>
+      </c>
+      <c r="F38" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="G38" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>61.2656</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1:01.27</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>59.9949</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.1004</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2176.7763</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>36:16.78</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:10;5:13;2:12;6:20;4:13;7:14;9:13;0:18;3:12;8:10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[5];5:[6];2:[5];6:[5,6];4:[6];7:[5];9:[7];0:[6];3:[9];8:[5]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[5]; c5:bw=13,experts=[6]; c2:bw=12,experts=[5]; c6:bw=20,experts=[5,6]; c4:bw=13,experts=[6]; c7:bw=14,experts=[5]; c9:bw=13,experts=[7]; c0:bw=18,experts=[6]; c3:bw=12,experts=[9]; c8:bw=10,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>4.9040,7.2967,4.2989,7.8671,7.9817,5.4445,4.1968,5.6427,6.1123,6.2502</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:13:53</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.870281435126298</v>
+      </c>
+      <c r="F39" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="G39" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="H39" t="n">
+        <v>38</v>
+      </c>
+      <c r="I39" t="n">
+        <v>60.7926</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1:00.79</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>59.5394</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.0951</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2237.5942</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>37:17.59</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:15;6:10;4:17;1:10;5:10;2:10;3:13;7:17;9:10;0:13</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[6];6:[7];4:[7];1:[6];5:[7];2:[6];3:[10];7:[6];9:[8];0:[7]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=15,experts=[6]; c6:bw=10,experts=[7]; c4:bw=17,experts=[7]; c1:bw=10,experts=[6]; c5:bw=10,experts=[7]; c2:bw=10,experts=[6]; c3:bw=13,experts=[10]; c7:bw=17,experts=[6]; c9:bw=10,experts=[8]; c0:bw=13,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>6.2829,7.9637,7.9292,4.9741,7.3400,4.4933,5.8831,5.2504,4.0597,5.3628</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:14:53</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.853972899321165</v>
+      </c>
+      <c r="F40" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="G40" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="H40" t="n">
+        <v>39</v>
+      </c>
+      <c r="I40" t="n">
+        <v>60.5655</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1:00.57</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>59.2833</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2298.1867</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>38:18.19</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:10;0:10;1:15;7:13;6:10;8:15;2:12;4:12;9:10;5:20</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[11];0:[8];1:[7];7:[7];6:[8];8:[7];2:[7];4:[8];9:[9];5:[8,9]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[11]; c0:bw=10,experts=[8]; c1:bw=15,experts=[7]; c7:bw=13,experts=[7]; c6:bw=10,experts=[8]; c8:bw=15,experts=[7]; c2:bw=12,experts=[7]; c4:bw=12,experts=[8]; c9:bw=10,experts=[9]; c5:bw=20,experts=[8,9]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5.9748,5.5894,5.0650,5.1738,7.6194,6.1226,4.4051,7.8928,4.1220,7.3184</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:15:55</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.846922729652505</v>
+      </c>
+      <c r="F41" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="G41" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="H41" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" t="n">
+        <v>61.7533</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1:01.75</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>60.5107</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.0843</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2359.9657</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>39:19.97</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:10;1:14;5:11;6:15;2:20;7:20;3:10;4:10;9:13;0:12</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[8];1:[8];5:[12];6:[9];2:[8,9];7:[8,9];3:[12];4:[9];9:[10];0:[9]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[8]; c1:bw=14,experts=[8]; c5:bw=11,experts=[12]; c6:bw=15,experts=[9]; c2:bw=20,experts=[8,9]; c7:bw=20,experts=[8,9]; c3:bw=10,experts=[12]; c4:bw=10,experts=[9]; c9:bw=13,experts=[10]; c0:bw=12,experts=[9]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6.4073,5.2260,7.3494,7.8720,4.4743,5.4954,6.0420,7.9616,4.1287,5.5540</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:16:55</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.841887167661956</v>
+      </c>
+      <c r="F42" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="G42" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="H42" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" t="n">
+        <v>60.1773</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1:00.18</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>58.9346</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2420.1684</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>40:20.17</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:18;6:10;8:19;1:10;4:17;5:20;7:20;3:13;9:18;0:10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[11];6:[10];8:[9];1:[9];4:[11];5:[13,14];7:[10,12];3:[13];9:[11];0:[10]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=18,experts=[11]; c6:bw=10,experts=[10]; c8:bw=19,experts=[9]; c1:bw=10,experts=[9]; c4:bw=17,experts=[11]; c5:bw=20,experts=[13,14]; c7:bw=20,experts=[10,12]; c3:bw=13,experts=[13]; c9:bw=18,experts=[11]; c0:bw=10,experts=[10]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4.3933,7.5008,6.0237,5.0139,7.8546,7.1039,5.1904,6.0093,4.2157,5.6291</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:17:56</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.824120455143938</v>
+      </c>
+      <c r="F43" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="G43" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="H43" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" t="n">
+        <v>60.5011</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1:00.50</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>59.2774</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.0762</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2480.6969</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>41:20.70</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:17;1:16;3:16;9:17;6:11;0:10;7:10;4:18;8:14;2:13</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[15];1:[10];3:[14];9:[12];6:[11];0:[11];7:[13];4:[12];8:[11];2:[12]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=17,experts=[15]; c1:bw=16,experts=[10]; c3:bw=16,experts=[14]; c9:bw=17,experts=[12]; c6:bw=11,experts=[11]; c0:bw=10,experts=[11]; c7:bw=10,experts=[13]; c4:bw=18,experts=[12]; c8:bw=14,experts=[11]; c2:bw=13,experts=[12]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>7.3991,5.0784,6.1101,4.1818,7.7903,5.3491,5.1400,7.5907,6.2156,4.4224</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:18:57</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.820027248551615</v>
+      </c>
+      <c r="F44" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="G44" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="H44" t="n">
+        <v>43</v>
+      </c>
+      <c r="I44" t="n">
+        <v>61.3726</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:01.37</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>60.0968</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.1227</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2542.0948</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>42:22.09</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:18;1:19;2:17;8:15;9:11;7:10;4:11;6:10;3:20;0:10</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[16];1:[11];2:[13];8:[12];9:[13];7:[14];4:[13];6:[12];3:[16,18];0:[12]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=18,experts=[16]; c1:bw=19,experts=[11]; c2:bw=17,experts=[13]; c8:bw=15,experts=[12]; c9:bw=11,experts=[13]; c7:bw=10,experts=[14]; c4:bw=11,experts=[13]; c6:bw=10,experts=[12]; c3:bw=20,experts=[16,18]; c0:bw=10,experts=[12]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>7.1468,5.0967,4.5053,6.2448,4.1585,5.4254,7.8781,7.8912,6.1345,5.6155</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:19:58</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.814028273188053</v>
+      </c>
+      <c r="F45" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="G45" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>60.5319</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:00.53</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>59.2484</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.1257</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2602.6549</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>43:22.65</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:20;3:16;4:10;2:12;7:20;5:10;6:10;9:12;8:11;1:15</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[13,14];3:[19];4:[14];2:[14];7:[15,16];5:[18];6:[13];9:[14];8:[13];1:[12]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=20,experts=[13,14]; c3:bw=16,experts=[19]; c4:bw=10,experts=[14]; c2:bw=12,experts=[14]; c7:bw=20,experts=[15,16]; c5:bw=10,experts=[18]; c6:bw=10,experts=[13]; c9:bw=12,experts=[14]; c8:bw=11,experts=[13]; c1:bw=15,experts=[12]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5.4571,5.8918,7.5386,4.2461,5.2315,7.1390,7.7801,4.2391,6.4968,5.2281</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:20:58</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.79946273743632</v>
+      </c>
+      <c r="F46" t="n">
+        <v>51</v>
+      </c>
+      <c r="G46" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="H46" t="n">
+        <v>44</v>
+      </c>
+      <c r="I46" t="n">
+        <v>60.252</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:00.25</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>58.9845</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.1131</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2662.9342</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>44:22.93</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:18;0:12;3:20;4:20;7:12;2:16;9:10;6:10;5:15;1:19</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[14];0:[15];3:[21,22];4:[16,18];7:[18];2:[16];9:[16];6:[14];5:[19];1:[13]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=18,experts=[14]; c0:bw=12,experts=[15]; c3:bw=20,experts=[21,22]; c4:bw=20,experts=[16,18]; c7:bw=12,experts=[18]; c2:bw=16,experts=[16]; c9:bw=10,experts=[16]; c6:bw=10,experts=[14]; c5:bw=15,experts=[19]; c1:bw=19,experts=[13]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6.4705,5.4825,5.8284,7.6766,5.2227,4.2868,3.9469,7.6782,7.2869,5.1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:21:59</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.787066389831542</v>
+      </c>
+      <c r="F47" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="G47" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>60.9783</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:00.98</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>59.7621</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2723.9392</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>45:23.94</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:12;3:10;6:13;1:14;4:20;5:14;2:19;8:13;0:18;7:10</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[18];3:[23];6:[15];1:[14];4:[19,21];5:[21];2:[18];8:[15];0:[16];7:[19]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=12,experts=[18]; c3:bw=10,experts=[23]; c6:bw=13,experts=[15]; c1:bw=14,experts=[14]; c4:bw=20,experts=[19,21]; c5:bw=14,experts=[21]; c2:bw=19,experts=[18]; c8:bw=13,experts=[15]; c0:bw=18,experts=[16]; c7:bw=10,experts=[19]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>4.1416,6.1206,7.8562,5.0499,7.9900,7.1952,4.3760,6.3021,5.5020,5.2286</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:23:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.78057296977044</v>
+      </c>
+      <c r="F48" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="G48" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" t="n">
+        <v>61.1054</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:01.11</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>59.8841</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2785.0717</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>46:25.07</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:17;6:10;7:18;9:10;8:13;3:20;4:10;0:15;1:10;2:18</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[22];6:[16];7:[21];9:[19];8:[16];3:[24,25];4:[22];0:[18];1:[15];2:[19]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=17,experts=[22]; c6:bw=10,experts=[16]; c7:bw=18,experts=[21]; c9:bw=10,experts=[19]; c8:bw=13,experts=[16]; c3:bw=20,experts=[24,25]; c4:bw=10,experts=[22]; c0:bw=15,experts=[18]; c1:bw=10,experts=[15]; c2:bw=18,experts=[19]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>7.0438,7.5357,5.2711,4.1909,6.2382,6.2516,8.2033,5.7538,5.1342,4.2615</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:24:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.776297434083772</v>
+      </c>
+      <c r="F49" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="G49" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="H49" t="n">
+        <v>46</v>
+      </c>
+      <c r="I49" t="n">
+        <v>60.1529</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:00.15</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>58.9139</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.0856</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2845.2533</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>47:25.25</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:17;8:17;4:20;2:19;9:17;6:15;5:18;7:20;0:10;3:10</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[16];8:[18];4:[23,24];2:[21];9:[21];6:[18];5:[23];7:[22,23];0:[19];3:[26]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=17,experts=[16]; c8:bw=17,experts=[18]; c4:bw=20,experts=[23,24]; c2:bw=19,experts=[21]; c9:bw=17,experts=[21]; c6:bw=15,experts=[18]; c5:bw=18,experts=[23]; c7:bw=20,experts=[22,23]; c0:bw=10,experts=[19]; c3:bw=10,experts=[26]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>4.9110,6.0877,7.5872,4.2069,3.9520,7.8084,7.3697,5.4510,5.4512,6.0888</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/exp09-c100-vgg11-e32-k12-posthoc/20260925-043635/rounds.xlsx
+++ b/results/exp09-c100-vgg11-e32-k12-posthoc/20260925-043635/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4519,6 +4519,4322 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:25:01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.770757535270381</v>
+      </c>
+      <c r="F50" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="G50" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49</v>
+      </c>
+      <c r="I50" t="n">
+        <v>60.2604</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1:00.26</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>59.0691</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.0467</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2905.746</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>48:25.75</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:16;3:11;8:10;0:10;2:19;5:19;6:10;7:15;9:18;1:18</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[25];3:[27];8:[19];0:[21];2:[22];5:[24];6:[19];7:[24];9:[22];1:[18]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=16,experts=[25]; c3:bw=11,experts=[27]; c8:bw=10,experts=[19]; c0:bw=10,experts=[21]; c2:bw=19,experts=[22]; c5:bw=19,experts=[24]; c6:bw=10,experts=[19]; c7:bw=15,experts=[24]; c9:bw=18,experts=[22]; c1:bw=18,experts=[18]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7.9173,6.0484,6.2048,5.4086,4.3923,7.2922,7.6807,5.2602,3.9837,4.8809</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:26:02</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.761611189474634</v>
+      </c>
+      <c r="F51" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="G51" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="H51" t="n">
+        <v>49</v>
+      </c>
+      <c r="I51" t="n">
+        <v>60.6834</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:00.68</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>59.4575</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2966.5576</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>49:26.56</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:11;4:10;7:11;6:20;2:20;1:20;3:13;0:10;9:10;5:10</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[21];4:[26];7:[25];6:[21,22];2:[23,24];1:[19,21];3:[28];0:[22];9:[23];5:[25]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=11,experts=[21]; c4:bw=10,experts=[26]; c7:bw=11,experts=[25]; c6:bw=20,experts=[21,22]; c2:bw=20,experts=[23,24]; c1:bw=20,experts=[19,21]; c3:bw=13,experts=[28]; c0:bw=10,experts=[22]; c9:bw=10,experts=[23]; c5:bw=10,experts=[25]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>5.9054,7.8194,5.4970,8.0801,4.5266,5.1954,6.0369,5.2949,4.0392,7.0625</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:27:02</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.754638189331008</v>
+      </c>
+      <c r="F52" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>51</v>
+      </c>
+      <c r="I52" t="n">
+        <v>60.0855</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:00.09</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>58.8445</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.0779</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3026.6699</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>50:26.67</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:16;0:18;1:10;2:10;8:15;6:17;9:10;3:18;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[26];0:[23];1:[22];2:[25];8:[22];6:[23];9:[24];3:[29];4:[27];7:[26]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=16,experts=[26]; c0:bw=18,experts=[23]; c1:bw=10,experts=[22]; c2:bw=10,experts=[25]; c8:bw=15,experts=[22]; c6:bw=17,experts=[23]; c9:bw=10,experts=[24]; c3:bw=18,experts=[29]; c4:bw=10,experts=[27]; c7:bw=10,experts=[26]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>7.0965,5.3721,4.9524,4.3010,6.0709,7.7520,4.1232,5.9216,7.8520,5.4028</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:28:02</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.747121785105225</v>
+      </c>
+      <c r="F53" t="n">
+        <v>52.06</v>
+      </c>
+      <c r="G53" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>51</v>
+      </c>
+      <c r="I53" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0:59.83</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>58.5808</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.0911</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3086.5304</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>51:26.53</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:15;8:10;5:10;7:11;1:13;4:11;9:10;6:17;2:10;3:14</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[24];8:[23];5:[27];7:[27];1:[23];4:[28];9:[25];6:[24];2:[26];3:[30]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=15,experts=[24]; c8:bw=10,experts=[23]; c5:bw=10,experts=[27]; c7:bw=11,experts=[27]; c1:bw=13,experts=[23]; c4:bw=11,experts=[28]; c9:bw=10,experts=[25]; c6:bw=17,experts=[24]; c2:bw=10,experts=[26]; c3:bw=14,experts=[30]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5.4837,6.2090,7.2190,5.2501,5.0250,7.8870,4.0197,7.4755,4.2809,5.7310</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:29:02</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.74231623927637</v>
+      </c>
+      <c r="F54" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="G54" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>51</v>
+      </c>
+      <c r="I54" t="n">
+        <v>60.5869</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:00.59</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>59.2835</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.1411</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3147.1435</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>52:27.14</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:10;4:10;5:15;1:20;3:16;9:20;6:12;7:15;0:13;2:17</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[24];4:[29];5:[28];1:[24,25];3:[31];9:[26,27];6:[25];7:[28];0:[25];2:[27]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[24]; c4:bw=10,experts=[29]; c5:bw=15,experts=[28]; c1:bw=20,experts=[24,25]; c3:bw=16,experts=[31]; c9:bw=20,experts=[26,27]; c6:bw=12,experts=[25]; c7:bw=15,experts=[28]; c0:bw=13,experts=[25]; c2:bw=17,experts=[27]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>6.1824,7.7330,7.0022,4.8456,5.8568,4.2100,7.8012,5.4071,5.5449,4.7002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:30:02</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.729590756580372</v>
+      </c>
+      <c r="F55" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="G55" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="H55" t="n">
+        <v>54</v>
+      </c>
+      <c r="I55" t="n">
+        <v>60.1178</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:00.12</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>58.8662</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.0914</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3207.2877</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>53:27.29</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:18;8:18;7:20;3:10;0:12;6:18;5:10;9:17;4:11</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[28];1:[26];8:[25];7:[29,30];3:[0];0:[26];6:[26];5:[29];9:[28];4:[30]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[28]; c1:bw=18,experts=[26]; c8:bw=18,experts=[25]; c7:bw=20,experts=[29,30]; c3:bw=10,experts=[0]; c0:bw=12,experts=[26]; c6:bw=18,experts=[26]; c5:bw=10,experts=[29]; c9:bw=17,experts=[28]; c4:bw=11,experts=[30]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4.5163,4.9604,6.0169,5.2380,5.9080,5.4730,7.7879,7.0539,3.9783,7.9333</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:31:03</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.726118757845834</v>
+      </c>
+      <c r="F56" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="G56" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55</v>
+      </c>
+      <c r="I56" t="n">
+        <v>60.5138</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:00.51</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>59.2734</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.0817</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3267.8305</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>54:27.83</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:18;2:14;4:10;3:17;8:10;5:18;1:20;6:14;0:10;9:20</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[31];2:[29];4:[31];3:[15];8:[26];5:[30];1:[27,28];6:[27];0:[27];9:[29,30]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=18,experts=[31]; c2:bw=14,experts=[29]; c4:bw=10,experts=[31]; c3:bw=17,experts=[15]; c8:bw=10,experts=[26]; c5:bw=18,experts=[30]; c1:bw=20,experts=[27,28]; c6:bw=14,experts=[27]; c0:bw=10,experts=[27]; c9:bw=20,experts=[29,30]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>5.3344,4.2931,7.7120,5.7365,6.1707,7.3600,5.0044,7.9305,5.5283,4.2035</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:32:03</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.720332438992979</v>
+      </c>
+      <c r="F57" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="G57" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="H57" t="n">
+        <v>55</v>
+      </c>
+      <c r="I57" t="n">
+        <v>60.1244</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:00.12</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>58.9127</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3327.9845</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>55:27.98</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:17;1:19;3:10;2:18;5:10;4:10;8:10;7:10;6:10;0:20</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[31];1:[29];3:[20];2:[30];5:[31];4:[15];8:[27];7:[11];6:[28];0:[28,29]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=17,experts=[31]; c1:bw=19,experts=[29]; c3:bw=10,experts=[20]; c2:bw=18,experts=[30]; c5:bw=10,experts=[31]; c4:bw=10,experts=[15]; c8:bw=10,experts=[27]; c7:bw=10,experts=[11]; c6:bw=10,experts=[28]; c0:bw=20,experts=[28,29]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>4.0941,4.8958,5.8927,4.3289,7.2093,7.7968,6.1484,5.3981,7.8011,5.3475</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:33:03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.747137186792055</v>
+      </c>
+      <c r="F58" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="G58" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="H58" t="n">
+        <v>55</v>
+      </c>
+      <c r="I58" t="n">
+        <v>60.2254</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1:00.23</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>58.9638</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.1064</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3388.2392</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>56:28.24</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:20;8:14;6:16;1:16;7:20;0:20;5:15;4:14;2:11;9:10</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[17,20];8:[28];6:[29];1:[30];7:[17,20];0:[30,31];5:[11];4:[10];2:[31];9:[0]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=20,experts=[17,20]; c8:bw=14,experts=[28]; c6:bw=16,experts=[29]; c1:bw=16,experts=[30]; c7:bw=20,experts=[17,20]; c0:bw=20,experts=[30,31]; c5:bw=15,experts=[11]; c4:bw=14,experts=[10]; c2:bw=11,experts=[31]; c9:bw=10,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>5.7583,5.9274,7.5010,4.9915,5.4014,5.5708,7.2744,8.0598,4.3566,4.1225</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:34:03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.72694007275356</v>
+      </c>
+      <c r="F59" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="G59" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="H59" t="n">
+        <v>55</v>
+      </c>
+      <c r="I59" t="n">
+        <v>60.0494</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1:00.05</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>58.8193</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.0895</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3448.3165</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>57:28.32</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:10;2:10;9:19;6:18;5:12;1:10;8:13;4:13;3:20;0:16</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[20];2:[15];9:[15];6:[30];5:[17];1:[31];8:[29];4:[17];3:[17,20];0:[17]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[20]; c2:bw=10,experts=[15]; c9:bw=19,experts=[15]; c6:bw=18,experts=[30]; c5:bw=12,experts=[17]; c1:bw=10,experts=[31]; c8:bw=13,experts=[29]; c4:bw=13,experts=[17]; c3:bw=20,experts=[17,20]; c0:bw=16,experts=[17]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>5.3994,4.2950,4.0288,7.7471,7.2324,4.9425,6.2573,7.8331,5.7500,5.3336</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:35:04</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.719132812711616</v>
+      </c>
+      <c r="F60" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="H60" t="n">
+        <v>55</v>
+      </c>
+      <c r="I60" t="n">
+        <v>60.6958</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1:00.70</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>59.445</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.1056</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3509.0418</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>58:29.04</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:12;8:19;9:10;6:10;1:20;4:10;7:10;5:11;0:17;3:12</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[10];8:[30];9:[17];6:[31];1:[17,20];4:[20];7:[20];5:[17];0:[20];3:[20]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=12,experts=[10]; c8:bw=19,experts=[30]; c9:bw=10,experts=[17]; c6:bw=10,experts=[31]; c1:bw=20,experts=[17,20]; c4:bw=10,experts=[20]; c7:bw=10,experts=[20]; c5:bw=11,experts=[17]; c0:bw=17,experts=[20]; c3:bw=12,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>4.3188,6.0944,4.1320,7.8237,5.0361,8.0940,5.4714,7.2106,5.4166,5.8474</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:35:59</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.701199611294825</v>
+      </c>
+      <c r="F61" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="G61" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="H61" t="n">
+        <v>55</v>
+      </c>
+      <c r="I61" t="n">
+        <v>54.6846</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0:54.68</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>53.6067</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.9271</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3563.7579</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>59:23.76</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:18;7:16;4:10;2:10;5:11;8:10;6:20;9:10;1:18;3:15</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[20];7:[20];4:[20];2:[17];5:[17];8:[31];6:[17,20];9:[20];1:[20];3:[20]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=18,experts=[20]; c7:bw=16,experts=[20]; c4:bw=10,experts=[20]; c2:bw=10,experts=[17]; c5:bw=11,experts=[17]; c8:bw=10,experts=[31]; c6:bw=20,experts=[17,20]; c9:bw=10,experts=[20]; c1:bw=18,experts=[20]; c3:bw=15,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>5.3837,5.1199,7.2436,3.6850,6.0776,5.5572,7.2537,3.7201,4.5396,5.0263</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:36:54</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.683041179691957</v>
+      </c>
+      <c r="F62" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="G62" t="n">
+        <v>53.37</v>
+      </c>
+      <c r="H62" t="n">
+        <v>61</v>
+      </c>
+      <c r="I62" t="n">
+        <v>55.1481</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0:55.15</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>53.9814</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.0134</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3618.9324</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:00:18.93</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:16;6:12;2:10;9:13;1:11;3:14;8:18;4:13;7:14;0:20</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[17];6:[20];2:[20];9:[20];1:[20];3:[20];8:[17];4:[20];7:[20];0:[17,20]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=16,experts=[17]; c6:bw=12,experts=[20]; c2:bw=10,experts=[20]; c9:bw=13,experts=[20]; c1:bw=11,experts=[20]; c3:bw=14,experts=[20]; c8:bw=18,experts=[17]; c4:bw=13,experts=[20]; c7:bw=14,experts=[20]; c0:bw=20,experts=[17,20]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>6.1739,6.6550,3.6911,3.5449,4.6862,5.5837,5.8428,7.4900,5.1137,5.2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:37:52</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.679045340205049</v>
+      </c>
+      <c r="F63" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="G63" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="H63" t="n">
+        <v>62</v>
+      </c>
+      <c r="I63" t="n">
+        <v>57.8803</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0:57.88</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>56.6873</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.0334</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3676.8381</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:01:16.84</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:10;6:20;9:10;4:20;5:20;0:10;3:18;2:14;1:20;7:15</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[10];6:[17,20];9:[20];4:[17,20];5:[17,20];0:[20];3:[20];2:[20];1:[17,20];7:[20]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[10]; c6:bw=20,experts=[17,20]; c9:bw=10,experts=[20]; c4:bw=20,experts=[17,20]; c5:bw=20,experts=[17,20]; c0:bw=10,experts=[20]; c3:bw=18,experts=[20]; c2:bw=14,experts=[20]; c1:bw=20,experts=[17,20]; c7:bw=15,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>5.8555,7.5537,4.0250,7.5795,6.8326,5.1359,5.6869,4.1478,4.7566,5.1138</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:38:49</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.663302280430123</v>
+      </c>
+      <c r="F64" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="G64" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H64" t="n">
+        <v>63</v>
+      </c>
+      <c r="I64" t="n">
+        <v>57.478</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0:57.48</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>56.2634</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1552</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.0585</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3734.3475</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:02:14.35</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:10;6:11;3:17;8:11;1:17;7:20;0:14;2:10;4:17</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[10];9:[20];6:[20];3:[20];8:[20];1:[20];7:[17,20];0:[20];2:[20];4:[20]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[10]; c9:bw=10,experts=[20]; c6:bw=11,experts=[20]; c3:bw=17,experts=[20]; c8:bw=11,experts=[20]; c1:bw=17,experts=[20]; c7:bw=20,experts=[17,20]; c0:bw=14,experts=[20]; c2:bw=10,experts=[20]; c4:bw=17,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>6.8879,4.0142,7.4874,5.6001,5.7797,4.7371,5.0310,5.0638,4.1174,7.5445</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:39:49</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.660049322698365</v>
+      </c>
+      <c r="F65" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H65" t="n">
+        <v>63</v>
+      </c>
+      <c r="I65" t="n">
+        <v>60.0016</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:00.00</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>58.7166</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1677</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.1164</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3794.3781</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:03:14.38</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:17;4:13;5:10;3:13;7:11;0:11;8:18;9:20;2:19;1:10</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[0];4:[0];5:[0];3:[1];7:[0];0:[0];8:[0];9:[1,20];2:[0];1:[0]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[0]; c4:bw=13,experts=[0]; c5:bw=10,experts=[0]; c3:bw=13,experts=[1]; c7:bw=11,experts=[0]; c0:bw=11,experts=[0]; c8:bw=18,experts=[0]; c9:bw=20,experts=[1,20]; c2:bw=19,experts=[0]; c1:bw=10,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>7.5465,7.7355,7.0123,5.5663,5.1592,5.4823,6.0894,4.2445,4.6082,5.2724</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:40:52</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.662300725107571</v>
+      </c>
+      <c r="F66" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="G66" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H66" t="n">
+        <v>63</v>
+      </c>
+      <c r="I66" t="n">
+        <v>62.9168</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:02.92</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>61.575</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.1565</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3857.3295</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:04:17.33</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:10;4:19;6:17;8:20;3:14;0:14;2:10;1:19;9:16</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[1];5:[1];4:[1];6:[1];8:[1,20];3:[2];0:[1];2:[1];1:[1];9:[2]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[1]; c5:bw=10,experts=[1]; c4:bw=19,experts=[1]; c6:bw=17,experts=[1]; c8:bw=20,experts=[1,20]; c3:bw=14,experts=[2]; c0:bw=14,experts=[1]; c2:bw=10,experts=[1]; c1:bw=19,experts=[1]; c9:bw=16,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>5.5513,7.4843,8.0050,7.8797,6.2688,6.2847,5.8307,4.6656,5.2955,4.3092</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:41:56</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.677024886361979</v>
+      </c>
+      <c r="F67" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="G67" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H67" t="n">
+        <v>63</v>
+      </c>
+      <c r="I67" t="n">
+        <v>63.9858</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:03.99</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>62.6861</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.1273</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3921.3453</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:05:21.35</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:14;5:10;1:18;8:10;9:10;6:10;4:14;0:13;3:20;7:17</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[2];5:[2];1:[2];8:[2];9:[3];6:[2];4:[2];0:[2];3:[3,4];7:[2]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=14,experts=[2]; c5:bw=10,experts=[2]; c1:bw=18,experts=[2]; c8:bw=10,experts=[2]; c9:bw=10,experts=[3]; c6:bw=10,experts=[2]; c4:bw=14,experts=[2]; c0:bw=13,experts=[2]; c3:bw=20,experts=[3,4]; c7:bw=17,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>4.6241,7.7578,5.3701,6.3929,4.2752,8.2334,8.3797,5.7283,6.2105,5.7141</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:43:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.661996015450403</v>
+      </c>
+      <c r="F68" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="G68" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H68" t="n">
+        <v>63</v>
+      </c>
+      <c r="I68" t="n">
+        <v>63.4376</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:03.44</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>62.1226</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.1432</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3984.8184</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:06:24.82</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:17;5:16;1:12;3:10;6:18;0:11;2:14;9:20;7:20;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[3];5:[3];1:[3];3:[5];6:[3];0:[3];2:[3];9:[4,5];7:[3,20];8:[3]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=17,experts=[3]; c5:bw=16,experts=[3]; c1:bw=12,experts=[3]; c3:bw=10,experts=[5]; c6:bw=18,experts=[3]; c0:bw=11,experts=[3]; c2:bw=14,experts=[3]; c9:bw=20,experts=[4,5]; c7:bw=20,experts=[3,20]; c8:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>8.1636,7.5787,5.2499,6.2441,8.1550,5.7926,4.6121,4.2366,5.5513,6.5387</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:44:04</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.681468930358745</v>
+      </c>
+      <c r="F69" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="G69" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H69" t="n">
+        <v>63</v>
+      </c>
+      <c r="I69" t="n">
+        <v>63.7659</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:03.77</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.1274</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4048.6195</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:07:28.62</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:14;8:10;2:19;0:10;3:10;4:16;5:15;9:10;7:10;6:11</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[4];8:[4];2:[4];0:[4];3:[6];4:[4];5:[4];9:[6];7:[4];6:[4]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=14,experts=[4]; c8:bw=10,experts=[4]; c2:bw=19,experts=[4]; c0:bw=10,experts=[4]; c3:bw=10,experts=[6]; c4:bw=16,experts=[4]; c5:bw=15,experts=[4]; c9:bw=10,experts=[6]; c7:bw=10,experts=[4]; c6:bw=11,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>5.2893,6.6408,4.6013,5.6407,6.2591,8.2608,7.5872,4.2950,5.6867,8.1992</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:45:07</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.665568600582635</v>
+      </c>
+      <c r="F70" t="n">
+        <v>36</v>
+      </c>
+      <c r="G70" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H70" t="n">
+        <v>63</v>
+      </c>
+      <c r="I70" t="n">
+        <v>63.6045</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:03.60</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>62.2984</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.1384</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4112.26</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:08:32.26</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:14;7:19;1:10;4:14;9:12;5:13;0:17;2:20;8:14;6:10</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[7];7:[5];1:[5];4:[5];9:[7];5:[5];0:[5];2:[5,20];8:[5];6:[5]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=14,experts=[7]; c7:bw=19,experts=[5]; c1:bw=10,experts=[5]; c4:bw=14,experts=[5]; c9:bw=12,experts=[7]; c5:bw=13,experts=[5]; c0:bw=17,experts=[5]; c2:bw=20,experts=[5,20]; c8:bw=14,experts=[5]; c6:bw=10,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>6.1683,5.4805,5.1542,8.3709,4.3803,7.4948,5.7591,4.6880,6.6953,8.1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:46:11</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.660753845146419</v>
+      </c>
+      <c r="F71" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="G71" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H71" t="n">
+        <v>63</v>
+      </c>
+      <c r="I71" t="n">
+        <v>63.5127</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:03.51</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>62.2285</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.1143</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4175.8064</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:09:35.81</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:10;9:10;7:10;3:11;0:10;6:10;2:18;4:19;5:10;8:16</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[6];9:[8];7:[6];3:[8];0:[6];6:[6];2:[6];4:[6];5:[6];8:[6]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[6]; c9:bw=10,experts=[8]; c7:bw=10,experts=[6]; c3:bw=11,experts=[8]; c0:bw=10,experts=[6]; c6:bw=10,experts=[6]; c2:bw=18,experts=[6]; c4:bw=19,experts=[6]; c5:bw=10,experts=[6]; c8:bw=16,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>5.1954,4.3411,5.6799,6.3254,5.7553,8.1612,4.6389,8.3587,7.4619,6.3107</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:47:14</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.643669406066268</v>
+      </c>
+      <c r="F72" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="G72" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H72" t="n">
+        <v>63</v>
+      </c>
+      <c r="I72" t="n">
+        <v>63.2516</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:03.25</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>61.9417</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.1443</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4239.0944</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:10:39.09</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:14;0:10;1:17;9:13;7:10;5:11;3:20;6:17;8:13;2:20</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[7];0:[7];1:[7];9:[9];7:[7];5:[7];3:[9,10];6:[7];8:[7];2:[7,20]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=14,experts=[7]; c0:bw=10,experts=[7]; c1:bw=17,experts=[7]; c9:bw=13,experts=[9]; c7:bw=10,experts=[7]; c5:bw=11,experts=[7]; c3:bw=20,experts=[9,10]; c6:bw=17,experts=[7]; c8:bw=13,experts=[7]; c2:bw=20,experts=[7,20]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>8.2084,5.6575,5.0854,4.1580,5.5565,7.7232,6.3477,8.1123,6.4434,4.6493</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:48:18</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.638298748094034</v>
+      </c>
+      <c r="F73" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="G73" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H73" t="n">
+        <v>63</v>
+      </c>
+      <c r="I73" t="n">
+        <v>63.7149</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:03.71</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>62.4057</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.1451</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4302.8472</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:11:42.85</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:10;1:13;5:14;7:16;6:10;0:17;3:10;2:10;9:13;4:13</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[8];1:[8];5:[8];7:[8];6:[8];0:[8];3:[11];2:[8];9:[10];4:[8]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[8]; c1:bw=13,experts=[8]; c5:bw=14,experts=[8]; c7:bw=16,experts=[8]; c6:bw=10,experts=[8]; c0:bw=17,experts=[8]; c3:bw=10,experts=[11]; c2:bw=10,experts=[8]; c9:bw=13,experts=[10]; c4:bw=13,experts=[8]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>6.4252,5.2018,7.5578,5.6848,8.2432,5.7034,6.2799,4.5883,4.3820,8.3393</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:49:22</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.640910866483215</v>
+      </c>
+      <c r="F74" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="G74" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H74" t="n">
+        <v>63</v>
+      </c>
+      <c r="I74" t="n">
+        <v>63.7948</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:03.79</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>62.4665</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4366.6765</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:12:46.68</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:16;8:10;3:13;1:20;5:10;9:17;0:10;7:12;6:10;4:14</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[9];8:[9];3:[12];1:[9,20];5:[9];9:[11];0:[9];7:[9];6:[9];4:[9]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=16,experts=[9]; c8:bw=10,experts=[9]; c3:bw=13,experts=[12]; c1:bw=20,experts=[9,20]; c5:bw=10,experts=[9]; c9:bw=17,experts=[11]; c0:bw=10,experts=[9]; c7:bw=12,experts=[9]; c6:bw=10,experts=[9]; c4:bw=14,experts=[9]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>4.5290,6.5013,6.4103,5.2639,7.5053,4.3669,5.7502,5.7384,8.2660,8.1352</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:50:25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.632475069590317</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H75" t="n">
+        <v>63</v>
+      </c>
+      <c r="I75" t="n">
+        <v>63.1016</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:03.10</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>61.8286</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1064</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4429.8176</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:13:49.82</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:13;1:10;5:17;7:20;8:10;6:10;2:10;4:16;9:11</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[13];0:[10];1:[10];5:[12];7:[10,12];8:[11];6:[10];2:[11];4:[11];9:[12]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[13]; c0:bw=13,experts=[10]; c1:bw=10,experts=[10]; c5:bw=17,experts=[12]; c7:bw=20,experts=[10,12]; c8:bw=10,experts=[11]; c6:bw=10,experts=[10]; c2:bw=10,experts=[11]; c4:bw=16,experts=[11]; c9:bw=11,experts=[12]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>6.2239,5.5667,5.0760,7.4158,5.5574,6.5071,8.2374,4.5889,8.3629,4.2924</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:51:28</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.629252285619572</v>
+      </c>
+      <c r="F76" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="G76" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H76" t="n">
+        <v>63</v>
+      </c>
+      <c r="I76" t="n">
+        <v>62.6268</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:02.63</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>61.3671</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.0989</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4492.4784</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:14:52.48</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:13;9:20;1:18;3:10;7:10;6:19;5:10;4:19;0:20;8:18</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[12];9:[13,20];1:[11];3:[14];7:[13];6:[11];5:[13];4:[12];0:[11,12];8:[12]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=13,experts=[12]; c9:bw=20,experts=[13,20]; c1:bw=18,experts=[11]; c3:bw=10,experts=[14]; c7:bw=10,experts=[13]; c6:bw=19,experts=[11]; c5:bw=10,experts=[13]; c4:bw=19,experts=[12]; c0:bw=20,experts=[11,12]; c8:bw=18,experts=[12]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>4.4042,4.1694,5.0734,6.0727,5.5808,8.2907,7.5317,8.2556,5.6670,6.3216</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:52:31</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.612681669818701</v>
+      </c>
+      <c r="F77" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="G77" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H77" t="n">
+        <v>63</v>
+      </c>
+      <c r="I77" t="n">
+        <v>62.9135</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:02.91</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>61.6381</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.1073</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4555.4307</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:15:55.43</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:10;5:12;0:10;3:10;2:10;6:10;7:20;4:20;9:19;1:18</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[13];5:[14];0:[13];3:[16];2:[13];6:[12];7:[14,15];4:[13,14];9:[14];1:[12]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[13]; c5:bw=12,experts=[14]; c0:bw=10,experts=[13]; c3:bw=10,experts=[16]; c2:bw=10,experts=[13]; c6:bw=10,experts=[12]; c7:bw=20,experts=[14,15]; c4:bw=20,experts=[13,14]; c9:bw=19,experts=[14]; c1:bw=18,experts=[12]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>6.2238,7.4276,5.7165,6.2839,4.7060,8.2149,5.5397,8.1320,4.2373,5.1562</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:53:34</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.595788757223295</v>
+      </c>
+      <c r="F78" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="G78" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H78" t="n">
+        <v>63</v>
+      </c>
+      <c r="I78" t="n">
+        <v>63.5627</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:03.56</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>62.2574</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.1288</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4619.0332</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:16:59.03</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:10;2:11;1:20;8:10;4:10;7:10;6:19;0:20;3:13;5:20</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[16];2:[14];1:[13,20];8:[14];4:[16];7:[16];6:[13];0:[14,15];3:[18];5:[15,16]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=10,experts=[16]; c2:bw=11,experts=[14]; c1:bw=20,experts=[13,20]; c8:bw=10,experts=[14]; c4:bw=10,experts=[16]; c7:bw=10,experts=[16]; c6:bw=19,experts=[13]; c0:bw=20,experts=[14,15]; c3:bw=13,experts=[18]; c5:bw=20,experts=[15,16]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>4.2392,4.6181,5.2928,6.7653,8.4276,5.5549,8.0761,5.6551,6.1835,7.4446</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:54:37</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.611117410083984</v>
+      </c>
+      <c r="F79" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H79" t="n">
+        <v>63</v>
+      </c>
+      <c r="I79" t="n">
+        <v>63.3119</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1:03.31</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>61.9807</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.1687</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4682.3836</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:18:02.38</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:10;4:10;3:13;7:12;8:18;1:14;9:10;6:19;5:20;2:11</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[16];4:[18];3:[19];7:[18];8:[15];1:[14];9:[18];6:[14];5:[18,19];2:[16]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=10,experts=[16]; c4:bw=10,experts=[18]; c3:bw=13,experts=[19]; c7:bw=12,experts=[18]; c8:bw=18,experts=[15]; c1:bw=14,experts=[14]; c9:bw=10,experts=[18]; c6:bw=19,experts=[14]; c5:bw=20,experts=[18,19]; c2:bw=11,experts=[16]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>5.8164,8.4135,6.3773,5.5603,6.2641,5.1044,4.2414,8.0777,7.4595,4.6661</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:55:41</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.599140689278777</v>
+      </c>
+      <c r="F80" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="G80" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H80" t="n">
+        <v>63</v>
+      </c>
+      <c r="I80" t="n">
+        <v>63.866</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:03.87</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>62.5325</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.1692</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4746.3875</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:19:06.39</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:10;9:10;0:12;4:20;7:15;8:15;5:18;3:10;1:12;2:11</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[15];9:[19];0:[18];4:[19,21];7:[19];8:[16];5:[21];3:[21];1:[15];2:[18]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=10,experts=[15]; c9:bw=10,experts=[19]; c0:bw=12,experts=[18]; c4:bw=20,experts=[19,21]; c7:bw=15,experts=[19]; c8:bw=15,experts=[16]; c5:bw=18,experts=[21]; c3:bw=10,experts=[21]; c1:bw=12,experts=[15]; c2:bw=11,experts=[18]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>8.3398,4.3622,5.7655,8.1781,5.5788,6.3476,7.3915,6.2514,5.5221,4.7955</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:56:45</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.594912046158971</v>
+      </c>
+      <c r="F81" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="G81" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H81" t="n">
+        <v>63</v>
+      </c>
+      <c r="I81" t="n">
+        <v>63.3059</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:03.31</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>61.9853</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.1577</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4809.7315</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:20:09.73</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:20;9:18;7:16;1:10;3:10;4:19;2:15;0:16;6:13;8:17</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[22,23];9:[21];7:[21];1:[16];3:[22];4:[22];2:[19];0:[19];6:[16];8:[18]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=20,experts=[22,23]; c9:bw=18,experts=[21]; c7:bw=16,experts=[21]; c1:bw=10,experts=[16]; c3:bw=10,experts=[22]; c4:bw=19,experts=[22]; c2:bw=15,experts=[19]; c0:bw=16,experts=[19]; c6:bw=13,experts=[16]; c8:bw=17,experts=[18]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>7.6376,4.3252,5.6824,5.2464,6.1726,8.1309,4.5049,5.7739,8.1564,6.3549</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:57:48</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.590046052079098</v>
+      </c>
+      <c r="F82" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="G82" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H82" t="n">
+        <v>63</v>
+      </c>
+      <c r="I82" t="n">
+        <v>63.6155</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:03.62</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>62.2883</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.1523</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4873.3861</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:21:13.39</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:17;2:15;3:20;1:16;4:14;5:10;9:10;7:19;8:16;0:17</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[18];2:[21];3:[23,24];1:[18];4:[23];5:[24];9:[22];7:[22];8:[19];0:[21]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[18]; c2:bw=15,experts=[21]; c3:bw=20,experts=[23,24]; c1:bw=16,experts=[18]; c4:bw=14,experts=[23]; c5:bw=10,experts=[24]; c9:bw=10,experts=[22]; c7:bw=19,experts=[22]; c8:bw=16,experts=[19]; c0:bw=17,experts=[21]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>8.1865,4.6038,6.1520,5.1682,8.1474,7.7445,4.4077,5.7463,6.4567,5.6752</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:58:52</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.583638832308752</v>
+      </c>
+      <c r="F83" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="G83" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H83" t="n">
+        <v>63</v>
+      </c>
+      <c r="I83" t="n">
+        <v>63.776</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:03.78</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>62.4583</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.1448</v>
+      </c>
+      <c r="N83" t="n">
+        <v>4937.2049</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:22:17.20</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:20;0:10;6:12;8:19;7:13;3:13;2:10;9:19;5:13;4:10</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[19,21];0:[22];6:[19];8:[21];7:[23];3:[25];2:[22];9:[23];5:[25];4:[24]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=20,experts=[19,21]; c0:bw=10,experts=[22]; c6:bw=12,experts=[19]; c8:bw=19,experts=[21]; c7:bw=13,experts=[23]; c3:bw=13,experts=[25]; c2:bw=10,experts=[22]; c9:bw=19,experts=[23]; c5:bw=13,experts=[25]; c4:bw=10,experts=[24]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>5.2795,5.6536,7.9771,6.4154,5.7078,6.5387,4.6750,4.3215,7.5987,8.2909</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:59:56</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.581019216300729</v>
+      </c>
+      <c r="F84" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="G84" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H84" t="n">
+        <v>63</v>
+      </c>
+      <c r="I84" t="n">
+        <v>63.4133</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:03.41</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>62.1396</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.1208</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5000.6578</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:23:20.66</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:17;4:10;2:14;7:12;5:10;0:10;6:18;1:20;8:13;3:14</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[24];4:[25];2:[23];7:[24];5:[26];0:[23];6:[21];1:[20,22];8:[22];3:[26]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=17,experts=[24]; c4:bw=10,experts=[25]; c2:bw=14,experts=[23]; c7:bw=12,experts=[24]; c5:bw=10,experts=[26]; c0:bw=10,experts=[23]; c6:bw=18,experts=[21]; c1:bw=20,experts=[20,22]; c8:bw=13,experts=[22]; c3:bw=14,experts=[26]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>4.2894,8.2209,4.5933,5.6521,7.6295,5.6606,8.0485,5.1879,6.5674,6.2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:00:59</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.580297625541344</v>
+      </c>
+      <c r="F85" t="n">
+        <v>37.43</v>
+      </c>
+      <c r="G85" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H85" t="n">
+        <v>63</v>
+      </c>
+      <c r="I85" t="n">
+        <v>63.5427</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:03.54</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>62.2296</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.1472</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5064.2418</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:24:24.24</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:20;3:11;1:19;6:10;9:10;2:12;7:16;5:10;4:10;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[20,23];3:[27];1:[23];6:[22];9:[25];2:[24];7:[25];5:[27];4:[26];0:[24]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=20,experts=[20,23]; c3:bw=11,experts=[27]; c1:bw=19,experts=[23]; c6:bw=10,experts=[22]; c9:bw=10,experts=[25]; c2:bw=12,experts=[24]; c7:bw=16,experts=[25]; c5:bw=10,experts=[27]; c4:bw=10,experts=[26]; c0:bw=10,experts=[24]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>6.2847,6.2434,5.4495,8.2059,4.2757,4.5818,5.5904,7.4949,8.3427,5.7606</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:02:03</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.581643609996559</v>
+      </c>
+      <c r="F86" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="G86" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H86" t="n">
+        <v>63</v>
+      </c>
+      <c r="I86" t="n">
+        <v>63.2338</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:03.23</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>61.9161</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.1511</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5127.5164</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:25:27.52</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:13;2:15;8:20;6:14;1:19;4:14;9:19;3:17;5:10;7:10</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[25];2:[25];8:[20,24];6:[23];1:[24];4:[27];9:[26];3:[28];5:[28];7:[26]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=13,experts=[25]; c2:bw=15,experts=[25]; c8:bw=20,experts=[20,24]; c6:bw=14,experts=[23]; c1:bw=19,experts=[24]; c4:bw=14,experts=[27]; c9:bw=19,experts=[26]; c3:bw=17,experts=[28]; c5:bw=10,experts=[28]; c7:bw=10,experts=[26]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>5.8273,4.7337,6.4421,7.9079,5.1154,8.0357,4.2316,6.2560,7.7453,5.6212</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:03:06</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.579951494337291</v>
+      </c>
+      <c r="F87" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="G87" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H87" t="n">
+        <v>63</v>
+      </c>
+      <c r="I87" t="n">
+        <v>63.0525</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:03.05</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>61.835</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.0552</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5190.6098</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:26:30.61</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:16;8:10;2:10;6:18;0:10;4:10;7:15;3:10;1:20;9:14</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[29];8:[25];2:[26];6:[24];0:[26];4:[28];7:[27];3:[29];1:[25,26];9:[27]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=16,experts=[29]; c8:bw=10,experts=[25]; c2:bw=10,experts=[26]; c6:bw=18,experts=[24]; c0:bw=10,experts=[26]; c4:bw=10,experts=[28]; c7:bw=15,experts=[27]; c3:bw=10,experts=[29]; c1:bw=20,experts=[25,26]; c9:bw=14,experts=[27]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>7.5304,6.3786,4.4741,7.9129,5.5370,8.2381,5.6920,6.3959,5.4916,4.1844</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:04:07</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.56948261307856</v>
+      </c>
+      <c r="F88" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="G88" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H88" t="n">
+        <v>63</v>
+      </c>
+      <c r="I88" t="n">
+        <v>61.638</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:01.64</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>60.3424</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.1292</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5252.2831</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:27:32.28</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:10;2:20;7:10;5:10;6:20;3:20;4:11;9:12;8:15;0:12</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[27];2:[27,28];7:[28];5:[30];6:[25,26];3:[30,31];4:[29];9:[28];8:[26];0:[27]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[27]; c2:bw=20,experts=[27,28]; c7:bw=10,experts=[28]; c5:bw=10,experts=[30]; c6:bw=20,experts=[25,26]; c3:bw=20,experts=[30,31]; c4:bw=11,experts=[29]; c9:bw=12,experts=[28]; c8:bw=15,experts=[26]; c0:bw=12,experts=[27]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>4.8361,4.1394,5.0819,7.1519,7.7351,6.3453,8.3541,4.3604,6.6046,5.7336</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:05:11</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.565553797967318</v>
+      </c>
+      <c r="F89" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="G89" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H89" t="n">
+        <v>63</v>
+      </c>
+      <c r="I89" t="n">
+        <v>63.7127</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:03.71</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>62.4289</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.1207</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5316.0372</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:28:36.04</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:14;6:10;3:11;7:14;0:20;4:13;9:10;1:10;5:10;2:15</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[27];6:[27];3:[0];7:[29];0:[28,29];4:[30];9:[29];1:[28];5:[31];2:[29]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=14,experts=[27]; c6:bw=10,experts=[27]; c3:bw=11,experts=[0]; c7:bw=14,experts=[29]; c0:bw=20,experts=[28,29]; c4:bw=13,experts=[30]; c9:bw=10,experts=[29]; c1:bw=10,experts=[28]; c5:bw=10,experts=[31]; c2:bw=15,experts=[29]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>6.4119,8.1002,6.1964,5.6897,5.7871,8.2634,4.3957,5.3506,7.6997,4.5342</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:06:15</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.565154959908561</v>
+      </c>
+      <c r="F90" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="G90" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H90" t="n">
+        <v>63</v>
+      </c>
+      <c r="I90" t="n">
+        <v>63.385</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:03.39</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>62.1048</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.1324</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5379.4636</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:29:39.46</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:10;8:20;2:15;9:20;7:10;5:15;0:10;6:11;4:10;1:14</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[15];8:[20,28];2:[30];9:[30,31];7:[30];5:[11];0:[30];6:[28];4:[31];1:[29]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[15]; c8:bw=20,experts=[20,28]; c2:bw=15,experts=[30]; c9:bw=20,experts=[30,31]; c7:bw=10,experts=[30]; c5:bw=15,experts=[11]; c0:bw=10,experts=[30]; c6:bw=11,experts=[28]; c4:bw=10,experts=[31]; c1:bw=14,experts=[29]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>6.1026,6.3913,4.6466,4.3327,5.5585,7.7150,5.8827,8.1710,8.1751,5.1294</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:07:18</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.561478700274946</v>
+      </c>
+      <c r="F91" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="G91" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H91" t="n">
+        <v>63</v>
+      </c>
+      <c r="I91" t="n">
+        <v>63.2311</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:03.23</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>61.9732</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.1189</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5442.7381</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:30:42.74</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:20;1:10;3:12;9:20;0:20;6:10;2:10;5:10;8:17;4:12</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[11,31];1:[30];3:[17];9:[0,15];0:[20,31];6:[29];2:[31];5:[17];8:[29];4:[15]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=20,experts=[11,31]; c1:bw=10,experts=[30]; c3:bw=12,experts=[17]; c9:bw=20,experts=[0,15]; c0:bw=20,experts=[20,31]; c6:bw=10,experts=[29]; c2:bw=10,experts=[31]; c5:bw=10,experts=[17]; c8:bw=17,experts=[29]; c4:bw=12,experts=[15]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>5.6445,5.2632,6.1379,4.2657,5.8461,8.3605,4.5535,7.4223,6.3196,8.1598</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:08:21</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.560757784136167</v>
+      </c>
+      <c r="F92" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="G92" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="H92" t="n">
+        <v>63</v>
+      </c>
+      <c r="I92" t="n">
+        <v>63.0193</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:03.02</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>61.7277</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.1391</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5505.7991</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:31:45.80</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:17;9:12;5:17;7:17;3:13;4:18;0:10;6:10;2:10;8:10</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[31];9:[17];5:[17];7:[20];3:[20];4:[10];0:[20];6:[30];2:[15];8:[30]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=17,experts=[31]; c9:bw=12,experts=[17]; c5:bw=17,experts=[17]; c7:bw=17,experts=[20]; c3:bw=13,experts=[20]; c4:bw=18,experts=[10]; c0:bw=10,experts=[20]; c6:bw=10,experts=[30]; c2:bw=10,experts=[15]; c8:bw=10,experts=[30]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>5.1026,4.1811,7.5693,5.7746,6.2936,8.0792,5.5620,8.0655,4.6013,6.4986</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:09:25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.529063490001549</v>
+      </c>
+      <c r="F93" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="G93" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="H93" t="n">
+        <v>92</v>
+      </c>
+      <c r="I93" t="n">
+        <v>64.00539999999999</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:04.01</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>62.6528</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.1701</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5569.8485</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:32:49.85</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:10;7:11;1:10;0:10;8:10;6:15;9:19;2:10;5:20;4:10</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[20];7:[20];1:[20];0:[20];8:[31];6:[31];9:[20];2:[10];5:[10,17];4:[20]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[20]; c7:bw=11,experts=[20]; c1:bw=10,experts=[20]; c0:bw=10,experts=[20]; c8:bw=10,experts=[31]; c6:bw=15,experts=[31]; c9:bw=19,experts=[20]; c2:bw=10,experts=[10]; c5:bw=20,experts=[10,17]; c4:bw=10,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>6.3543,5.7904,5.3565,5.7374,6.4407,8.1322,4.3548,4.6573,7.5647,8.2645</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:10:29</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.512041706684784</v>
+      </c>
+      <c r="F94" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="G94" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="H94" t="n">
+        <v>93</v>
+      </c>
+      <c r="I94" t="n">
+        <v>64.23050000000001</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1:04.23</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>62.9219</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.1493</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5634.1213</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:33:54.12</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:16;3:10;7:10;9:19;6:10;8:10;5:10;4:11;0:10;2:17</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[20];3:[20];7:[20];9:[20];6:[20];8:[17];5:[17];4:[20];0:[17];2:[17]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=16,experts=[20]; c3:bw=10,experts=[20]; c7:bw=10,experts=[20]; c9:bw=19,experts=[20]; c6:bw=10,experts=[20]; c8:bw=10,experts=[17]; c5:bw=10,experts=[17]; c4:bw=11,experts=[20]; c0:bw=10,experts=[17]; c2:bw=17,experts=[17]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>5.3673,6.4032,5.6316,4.3031,8.3209,6.5389,7.6067,8.2717,5.7484,4.7300</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:11:32</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.502777714384617</v>
+      </c>
+      <c r="F95" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="G95" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="H95" t="n">
+        <v>93</v>
+      </c>
+      <c r="I95" t="n">
+        <v>62.9318</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:02.93</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>61.6434</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.1352</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5697.0971</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:34:57.10</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:15;2:20;5:14;4:10;6:10;9:17;1:20;8:10;0:18;3:11</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[20];2:[17,20];5:[20];4:[17];6:[17];9:[20];1:[17,20];8:[10];0:[20];3:[20]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=15,experts=[20]; c2:bw=20,experts=[17,20]; c5:bw=14,experts=[20]; c4:bw=10,experts=[17]; c6:bw=10,experts=[17]; c9:bw=17,experts=[20]; c1:bw=20,experts=[17,20]; c8:bw=10,experts=[10]; c0:bw=18,experts=[20]; c3:bw=11,experts=[20]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>5.6996,4.5874,7.5315,8.2447,7.8829,4.1636,5.1140,6.3483,5.7350,6.3362</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:12:36</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.495248665297207</v>
+      </c>
+      <c r="F96" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="G96" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="H96" t="n">
+        <v>95</v>
+      </c>
+      <c r="I96" t="n">
+        <v>63.2818</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:03.28</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>61.9598</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5760.4203</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:36:00.42</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:20;9:14;4:10;6:13;0:12;3:14;1:10;8:20;2:10;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[17,20];9:[20];4:[20];6:[20];0:[20];3:[20];1:[20];8:[17,20];2:[20];5:[17]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=20,experts=[17,20]; c9:bw=14,experts=[20]; c4:bw=10,experts=[20]; c6:bw=13,experts=[20]; c0:bw=12,experts=[20]; c3:bw=14,experts=[20]; c1:bw=10,experts=[20]; c8:bw=20,experts=[17,20]; c2:bw=10,experts=[20]; c5:bw=10,experts=[17]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>5.4695,4.2874,8.1348,7.8990,5.5207,6.2020,5.3771,6.6646,4.6489,7.7558</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:13:40</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.488729369254272</v>
+      </c>
+      <c r="F97" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="G97" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="H97" t="n">
+        <v>95</v>
+      </c>
+      <c r="I97" t="n">
+        <v>64.191</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:04.19</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>62.902</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.1422</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5824.6568</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:37:04.66</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:20;9:15;3:15;1:12;5:20;4:16;6:10;7:17;0:12;8:20</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,20];9:[1];3:[1];1:[0];5:[0,17];4:[0];6:[0];7:[0];0:[0];8:[0,20]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=20,experts=[0,20]; c9:bw=15,experts=[1]; c3:bw=15,experts=[1]; c1:bw=12,experts=[0]; c5:bw=20,experts=[0,17]; c4:bw=16,experts=[0]; c6:bw=10,experts=[0]; c7:bw=17,experts=[0]; c0:bw=12,experts=[0]; c8:bw=20,experts=[0,20]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>4.6899,4.3263,6.2122,5.2377,7.6047,8.4250,8.2985,5.7513,5.8091,6.5473</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:14:43</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.491756704841593</v>
+      </c>
+      <c r="F98" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="G98" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="H98" t="n">
+        <v>95</v>
+      </c>
+      <c r="I98" t="n">
+        <v>63.2098</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:03.21</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>62.015</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.0429</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5887.9108</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:38:07.91</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:14;9:14;8:14;4:10;7:10;1:17;3:12;5:15;6:17;2:18</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[1];9:[2];8:[1];4:[1];7:[1];1:[1];3:[2];5:[1];6:[1];2:[1]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=14,experts=[1]; c9:bw=14,experts=[2]; c8:bw=14,experts=[1]; c4:bw=10,experts=[1]; c7:bw=10,experts=[1]; c1:bw=17,experts=[1]; c3:bw=12,experts=[2]; c5:bw=15,experts=[1]; c6:bw=17,experts=[1]; c2:bw=18,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5.6811,4.3318,6.5711,8.3872,5.6669,5.3697,6.4721,7.8078,7.5929,4.1344</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:15:45</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.483623249485872</v>
+      </c>
+      <c r="F99" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="G99" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="H99" t="n">
+        <v>95</v>
+      </c>
+      <c r="I99" t="n">
+        <v>61.789</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:01.79</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>60.4991</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5949.7425</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:39:09.74</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:17;8:18;9:10;7:10;6:12;5:16;0:11;3:10;1:10;2:10</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[2];8:[2];9:[3];7:[2];6:[2];5:[2];0:[2];3:[3];1:[2];2:[2]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=17,experts=[2]; c8:bw=18,experts=[2]; c9:bw=10,experts=[3]; c7:bw=10,experts=[2]; c6:bw=12,experts=[2]; c5:bw=16,experts=[2]; c0:bw=11,experts=[2]; c3:bw=10,experts=[3]; c1:bw=10,experts=[2]; c2:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>7.5683,6.2967,4.1694,5.4123,8.1074,7.6151,5.6291,6.1146,5.1393,4.4469</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:16:48</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.480214080688716</v>
+      </c>
+      <c r="F100" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="G100" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="H100" t="n">
+        <v>95</v>
+      </c>
+      <c r="I100" t="n">
+        <v>63.1099</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:03.11</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>61.7859</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.1645</v>
+      </c>
+      <c r="N100" t="n">
+        <v>6012.897</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:40:12.90</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:11;5:16;7:15;1:20;3:13;9:10;4:10;0:13;2:10;6:12</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[3];5:[3];7:[3];1:[3,20];3:[4];9:[4];4:[3];0:[3];2:[3];6:[3]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=11,experts=[3]; c5:bw=16,experts=[3]; c7:bw=15,experts=[3]; c1:bw=20,experts=[3,20]; c3:bw=13,experts=[4]; c9:bw=10,experts=[4]; c4:bw=10,experts=[3]; c0:bw=13,experts=[3]; c2:bw=10,experts=[3]; c6:bw=12,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>6.4119,7.4926,5.5853,5.3122,6.2551,4.1864,8.0301,5.5717,4.6290,8.3116</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:17:54</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.496173918897229</v>
+      </c>
+      <c r="F101" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="G101" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="H101" t="n">
+        <v>95</v>
+      </c>
+      <c r="I101" t="n">
+        <v>65.53660000000001</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:05.54</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>64.2403</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.1419</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6078.4777</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:41:18.48</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:10;8:15;9:18;5:10;6:15;1:10;4:20;7:10;3:14;0:20</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[4];8:[4];9:[5];5:[4];6:[4];1:[4];4:[4,20];7:[4];3:[5];0:[4,20]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[4]; c8:bw=15,experts=[4]; c9:bw=18,experts=[5]; c5:bw=10,experts=[4]; c6:bw=15,experts=[4]; c1:bw=10,experts=[4]; c4:bw=20,experts=[4,20]; c7:bw=10,experts=[4]; c3:bw=14,experts=[5]; c0:bw=20,experts=[4,20]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>4.6238,6.8386,4.4797,7.7947,8.2077,5.4159,8.8428,5.7327,6.4634,5.8410</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
